--- a/Sample_run/1/student/nguyendvhe176752/TC2/GradeDetail.xlsx
+++ b/Sample_run/1/student/nguyendvhe176752/TC2/GradeDetail.xlsx
@@ -1041,7 +1041,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1100,7 +1100,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1153,7 +1153,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1268,7 +1268,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>55</x:v>
@@ -1324,7 +1324,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>55</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1436,7 +1436,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>55</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1548,7 +1548,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>35938</x:v>
+        <x:v>36276</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>55</x:v>
